--- a/data/trans_orig/IP07A08-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07A08-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse alegre en 2007 (tasa de respuesta: 99,6%)</t>
+          <t>Menores según la frecuencia de sentirse alegre, percibida por el adulto en 2007 (tasa de respuesta: 99,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24011</t>
+          <t>23846</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34597</t>
+          <t>34837</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19489</t>
+          <t>19764</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30437</t>
+          <t>30765</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47011</t>
+          <t>46437</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>62784</t>
+          <t>62626</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>63,97%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13029</t>
+          <t>12776</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23051</t>
+          <t>23383</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12943</t>
+          <t>12776</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23420</t>
+          <t>23096</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29108</t>
+          <t>28178</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43803</t>
+          <t>43638</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,57%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>638</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>5312</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7590</t>
+          <t>7367</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2593</t>
+          <t>2624</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10428</t>
+          <t>10136</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,35%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3463</t>
+          <t>3440</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4156</t>
+          <t>3992</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>4539</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3351</t>
+          <t>3590</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4132</t>
+          <t>3243</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>98700</t>
+          <t>99804</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>122283</t>
+          <t>121873</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>119454</t>
+          <t>119512</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>143372</t>
+          <t>144692</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>60,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>225311</t>
+          <t>224894</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>258842</t>
+          <t>259129</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>58,7%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>71085</t>
+          <t>70881</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94104</t>
+          <t>92820</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>83463</t>
+          <t>82120</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>106996</t>
+          <t>107236</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>159769</t>
+          <t>159753</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>193246</t>
+          <t>194313</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>44,02%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6565</t>
+          <t>5889</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16577</t>
+          <t>16619</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6574</t>
+          <t>7030</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17102</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>15340</t>
+          <t>14904</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>29165</t>
+          <t>29771</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3782</t>
+          <t>2768</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2735</t>
+          <t>3802</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24469</t>
+          <t>24640</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37994</t>
+          <t>37545</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24906</t>
+          <t>24682</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37575</t>
+          <t>37341</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52623</t>
+          <t>52813</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>70467</t>
+          <t>70465</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27020</t>
+          <t>26855</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>40430</t>
+          <t>39854</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19732</t>
+          <t>20757</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32988</t>
+          <t>33259</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>51395</t>
+          <t>51446</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>69872</t>
+          <t>69454</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>54,58%</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3449</t>
+          <t>3208</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>613</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4907</t>
+          <t>5898</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>680</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6102</t>
+          <t>6629</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3724</t>
+          <t>4855</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3860</t>
+          <t>3899</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4948</t>
+          <t>4261</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5029</t>
+          <t>4952</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>156476</t>
+          <t>157380</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>186549</t>
+          <t>187675</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>173491</t>
+          <t>171764</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>203150</t>
+          <t>201130</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>338134</t>
+          <t>338003</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>380208</t>
+          <t>378401</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>56,77%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>118213</t>
+          <t>117367</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>146656</t>
+          <t>148109</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>125050</t>
+          <t>125080</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>154384</t>
+          <t>154784</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>252198</t>
+          <t>253439</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>293464</t>
+          <t>294176</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>44,13%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8031</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>19664</t>
+          <t>19198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10789</t>
+          <t>10637</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23945</t>
+          <t>23672</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>22024</t>
+          <t>21278</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>38703</t>
+          <t>38267</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3442</t>
+          <t>3425</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>682</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6423</t>
+          <t>6039</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>805</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7481</t>
+          <t>7854</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5573</t>
+          <t>5581</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>649</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5546</t>
+          <t>5949</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse alegre en 2012 (tasa de respuesta: 98,12%)</t>
+          <t>Menores según la frecuencia de sentirse alegre, percibida por el adulto en 2012 (tasa de respuesta: 98,12%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25879</t>
+          <t>25960</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37581</t>
+          <t>37525</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16961</t>
+          <t>17321</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27815</t>
+          <t>27473</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45694</t>
+          <t>45671</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>62434</t>
+          <t>62161</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>62,83%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14721</t>
+          <t>15066</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26333</t>
+          <t>26529</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16855</t>
+          <t>16803</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27854</t>
+          <t>27527</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,75%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34942</t>
+          <t>35155</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51105</t>
+          <t>51076</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>51,63%</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4178</t>
+          <t>4435</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>3704</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3972,7 +3972,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4784</t>
+          <t>4133</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4007,7 +4007,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3117</t>
+          <t>3721</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3338</t>
+          <t>3123</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>108208</t>
+          <t>108181</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>131840</t>
+          <t>131865</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>64,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>120082</t>
+          <t>120938</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>145475</t>
+          <t>144448</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>52,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>234754</t>
+          <t>234767</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>269638</t>
+          <t>270033</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>62,19%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67904</t>
+          <t>68465</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>90639</t>
+          <t>91096</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>72467</t>
+          <t>72015</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>96060</t>
+          <t>95770</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>147262</t>
+          <t>145886</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>180493</t>
+          <t>180138</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,49%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1225</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7745</t>
+          <t>7650</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4412</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13249</t>
+          <t>13182</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>6881</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>18263</t>
+          <t>18112</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>693</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6163</t>
+          <t>6503</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>577</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5852</t>
+          <t>5159</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>1473</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8896</t>
+          <t>8548</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3261</t>
+          <t>3070</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>603</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5381</t>
+          <t>5857</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>693</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6923</t>
+          <t>6311</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31816</t>
+          <t>31478</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45036</t>
+          <t>44835</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26676</t>
+          <t>27205</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39323</t>
+          <t>39103</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>62430</t>
+          <t>62569</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>80542</t>
+          <t>80810</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,59%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14756</t>
+          <t>14667</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27627</t>
+          <t>27484</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15328</t>
+          <t>15486</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27601</t>
+          <t>27072</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>33375</t>
+          <t>33522</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51019</t>
+          <t>50327</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>41,47%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1395</t>
+          <t>1413</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8005</t>
+          <t>7914</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1414</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7966</t>
+          <t>7728</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3721</t>
+          <t>3740</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12747</t>
+          <t>13083</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,78%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>175415</t>
+          <t>176647</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>204360</t>
+          <t>205297</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>54,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>174190</t>
+          <t>173078</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>202715</t>
+          <t>202939</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,47 +5787,47 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
+          <t>61,03%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>548</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>378656</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>357244</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>399052</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>57,86%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>54,59%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
           <t>60,97%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>548</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>378656</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>358158</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>398169</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>57,86%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>54,73%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>60,84%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>107566</t>
+          <t>106485</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>134727</t>
+          <t>135861</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>113575</t>
+          <t>112876</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>142749</t>
+          <t>141458</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>229339</t>
+          <t>228213</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>267692</t>
+          <t>269308</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>41,15%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4153</t>
+          <t>4471</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12639</t>
+          <t>13748</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7334</t>
+          <t>7347</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>18771</t>
+          <t>19014</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>13150</t>
+          <t>13449</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>27865</t>
+          <t>28805</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -6081,7 +6081,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6365</t>
+          <t>6061</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>686</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5873</t>
+          <t>6229</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9827</t>
+          <t>9660</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3299</t>
+          <t>3787</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>611</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>6302</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>664</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6534</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse alegre en 2016 (tasa de respuesta: 99,02%)</t>
+          <t>Menores según la frecuencia de sentirse alegre, percibida por el adulto en 2016 (tasa de respuesta: 99,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12762</t>
+          <t>13678</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22143</t>
+          <t>22564</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16845</t>
+          <t>16545</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26378</t>
+          <t>26376</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33103</t>
+          <t>32681</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46247</t>
+          <t>46320</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>67,67%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7449</t>
+          <t>6883</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16555</t>
+          <t>15497</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8826</t>
+          <t>9138</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18330</t>
+          <t>18524</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19121</t>
+          <t>18284</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32002</t>
+          <t>31280</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>45,7%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>574</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6192</t>
+          <t>6911</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5446</t>
+          <t>5892</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1381</t>
+          <t>1470</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8338</t>
+          <t>9015</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>13,17%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>123486</t>
+          <t>123157</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>149041</t>
+          <t>149790</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>120988</t>
+          <t>120911</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>145965</t>
+          <t>146853</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>251469</t>
+          <t>251849</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>288152</t>
+          <t>286980</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>57,72%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>87363</t>
+          <t>87927</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>112697</t>
+          <t>112790</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>89519</t>
+          <t>88987</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>114542</t>
+          <t>114234</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>183766</t>
+          <t>184517</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>219489</t>
+          <t>219289</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,1%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7159</t>
+          <t>7099</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17328</t>
+          <t>17971</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t>5473</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15803</t>
+          <t>15646</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>14411</t>
+          <t>14459</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>29428</t>
+          <t>28840</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4533</t>
+          <t>4999</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7711,7 +7711,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3633</t>
+          <t>3609</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5773</t>
+          <t>5590</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7761,7 +7761,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5095</t>
+          <t>5045</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7824,7 +7824,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4294</t>
+          <t>4167</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>723</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6676</t>
+          <t>6978</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28842</t>
+          <t>29170</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43492</t>
+          <t>42487</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>57,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38878</t>
+          <t>38184</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>52281</t>
+          <t>52852</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71259</t>
+          <t>70674</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>91977</t>
+          <t>91505</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>60,02%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27996</t>
+          <t>28544</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42760</t>
+          <t>42061</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25197</t>
+          <t>24698</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39196</t>
+          <t>39587</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>56657</t>
+          <t>56687</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>77684</t>
+          <t>77920</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>51,11%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>648</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6359</t>
+          <t>6396</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8280,7 +8280,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3870</t>
+          <t>3375</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7000</t>
+          <t>7047</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3554</t>
+          <t>3544</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>3556</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>173857</t>
+          <t>173862</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>204970</t>
+          <t>207589</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>185330</t>
+          <t>185167</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>217812</t>
+          <t>216944</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>370818</t>
+          <t>368485</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>413054</t>
+          <t>416148</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,95%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>132538</t>
+          <t>129555</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>163890</t>
+          <t>161904</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>129991</t>
+          <t>131102</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>162502</t>
+          <t>162355</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>271021</t>
+          <t>270428</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>314186</t>
+          <t>315271</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>43,9%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11123</t>
+          <t>10884</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>23640</t>
+          <t>24899</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7163</t>
+          <t>6901</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>18623</t>
+          <t>18660</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>20803</t>
+          <t>20622</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>38279</t>
+          <t>38192</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -9040,7 +9040,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5961</t>
+          <t>4629</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9075,7 +9075,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>3620</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9090,7 +9090,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5921</t>
+          <t>6008</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>661</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6289</t>
+          <t>5815</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9188,7 +9188,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4124</t>
+          <t>4740</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9203,7 +9203,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7619</t>
+          <t>7700</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP07A08-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07A08-Estudios-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse alegre, percibida por el adulto en 2007 (tasa de respuesta: 99,6%)</t>
+          <t>Menores según la frecuencia de sentirse alegre, percibida por el/la adulto/a [KIDSCREEN 20] en 2007 (tasa de respuesta: 99,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>25025</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>19457</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>30515</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>52,99%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>41,2%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>64,61%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>29612</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>23846</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>34837</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>23917</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>35401</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>58,44%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>47,06%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>68,75%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>25025</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>19764</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>30765</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>52,99%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>69,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46437</t>
+          <t>46409</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>62626</t>
+          <t>63303</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>64,66%</t>
         </is>
       </c>
     </row>
@@ -840,67 +840,67 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>17978</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12953</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>24435</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>38,07%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>27,43%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>51,74%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>17775</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>12776</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>23383</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>12383</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>23226</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>35,08%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>25,21%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>46,14%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>17978</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>12776</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>23096</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>38,07%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28178</t>
+          <t>28293</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43638</t>
+          <t>44364</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>45,31%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3425</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1311</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>7248</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>7,25%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2,78%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>15,35%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>1957</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>638</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5312</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>5346</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>3,86%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>10,48%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>3425</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1300</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>7367</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>7,25%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>2593</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10136</t>
+          <t>10236</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,46%</t>
         </is>
       </c>
     </row>
@@ -1066,102 +1066,102 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>802</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4671</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,89%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>683</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3440</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4333</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,35%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,79%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>802</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>8,55%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1485</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3992</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>5009</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>8,45%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1485</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4539</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -1174,107 +1174,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>647</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3590</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3239</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>1,28%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>7,08%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>6,39%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>3262</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>3243</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>47230</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>47230</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>47230</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>50674</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>50674</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>50674</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>47230</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>47230</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>47230</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>131337</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>119133</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>143803</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>55,19%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>50,06%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>60,43%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>110942</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>99804</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>121873</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>100155</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>122422</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>54,53%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>49,05%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>59,9%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>131337</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>119512</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>144692</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>55,19%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>224894</t>
+          <t>226759</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>259129</t>
+          <t>260412</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>58,99%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>94898</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>82472</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>106824</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>39,88%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>34,66%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>44,89%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>82019</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>70881</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>92820</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>71909</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>92354</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>40,31%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>34,84%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>45,62%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>94898</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>82120</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>107236</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>39,88%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>159753</t>
+          <t>159555</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>194313</t>
+          <t>192840</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>43,69%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>11049</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6537</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>16772</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>4,64%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2,75%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>7,05%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>10502</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>5889</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>16619</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>6051</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>16068</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>5,16%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,89%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>8,17%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>11049</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>7030</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>16882</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>4,64%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>14904</t>
+          <t>15455</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>29771</t>
+          <t>29387</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,66%</t>
         </is>
       </c>
     </row>
@@ -1743,107 +1743,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3868</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>679</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2768</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4081</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>679</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3802</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>237963</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>237963</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>237963</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>304</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>203463</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>203463</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>203463</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>359</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>237963</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>237963</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>237963</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>30790</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>24197</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>36719</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>50,98%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>40,07%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>60,8%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>31324</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>24640</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>37545</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>24623</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>37974</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>46,85%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>36,86%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>56,16%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>30790</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>24682</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>37341</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>50,98%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52813</t>
+          <t>52660</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>70465</t>
+          <t>70796</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>55,64%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>26779</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>20794</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>33036</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>44,34%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>34,43%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>54,7%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>33460</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>26855</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>39854</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>26909</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>40189</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>50,05%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>40,17%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>59,61%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>26779</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>20757</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>33259</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>44,34%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>51446</t>
+          <t>51556</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>69454</t>
+          <t>69405</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>54,54%</t>
         </is>
       </c>
     </row>
@@ -2312,72 +2312,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>5380</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3,33%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>8,91%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>654</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>3208</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>2731</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>0,98%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>4,8%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>5898</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>3,33%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>679</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6629</t>
+          <t>6289</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -2425,107 +2425,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>813</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>4734</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>7,84%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>813</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>4855</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>4054</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>8,04%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>813</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>3899</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -2538,92 +2538,92 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>1416</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4261</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>4392</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>2,12%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>6,37%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>6,57%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>1416</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>1416</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4952</t>
+          <t>4947</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>60394</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>60394</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>60394</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>66854</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>66854</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>66854</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>60394</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>60394</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>60394</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2768,72 +2768,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>187153</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>171952</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>202016</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>54,16%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>49,76%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>58,46%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>171878</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>157380</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>187675</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>158494</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>186093</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>53,55%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>49,03%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>58,47%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>187153</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>171764</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>201130</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>54,16%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>338003</t>
+          <t>338400</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>378401</t>
+          <t>378797</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>56,83%</t>
         </is>
       </c>
     </row>
@@ -2881,72 +2881,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>139655</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>124546</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>153196</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>40,41%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>36,04%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>44,33%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>198</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>133254</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>117367</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>148109</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>119334</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>146695</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>41,51%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>36,56%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>46,14%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>139655</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>125080</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>154784</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>40,41%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>253439</t>
+          <t>252055</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>294176</t>
+          <t>292945</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>43,95%</t>
         </is>
       </c>
     </row>
@@ -2994,72 +2994,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>16486</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>11268</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>24251</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>4,77%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>7,02%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>13113</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>8358</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>19198</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>8232</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>19115</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>4,09%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>5,98%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>16486</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>10637</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>23672</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>4,77%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>21278</t>
+          <t>21934</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>38267</t>
+          <t>38966</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -3107,74 +3107,74 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>2293</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>6234</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>683</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>3425</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3435</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,21%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
         <is>
           <t>1,07%</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>2293</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>682</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>6039</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>4</t>
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>688</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7854</t>
+          <t>7916</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -3220,72 +3220,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>2063</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>5581</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>5548</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,64%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>645</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5949</t>
+          <t>5510</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -3333,57 +3333,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>345587</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>345587</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>345587</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>476</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>320991</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>320991</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>320991</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>345587</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>345587</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>345587</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3496,13 +3496,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse alegre, percibida por el adulto en 2012 (tasa de respuesta: 98,12%)</t>
+          <t>Menores según la frecuencia de sentirse alegre, percibida por el/la adulto/a [KIDSCREEN 20] en 2012 (tasa de respuesta: 98,12%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3513,7 +3513,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3681,72 +3681,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>22345</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>17357</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>28290</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>48,73%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>37,85%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>61,7%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>31895</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>25960</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>37525</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>25229</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>37379</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>60,08%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>48,9%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>70,69%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>22345</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>17321</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>27473</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>48,73%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45671</t>
+          <t>45002</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>62161</t>
+          <t>61958</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>62,63%</t>
         </is>
       </c>
     </row>
@@ -3794,72 +3794,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>22277</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>16319</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>27497</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>48,58%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>35,59%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>59,97%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>20496</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>15066</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>26529</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>14799</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>27078</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>38,61%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>28,38%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>49,98%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>22277</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>16803</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>27527</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>48,58%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35155</t>
+          <t>35041</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51076</t>
+          <t>51548</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>52,1%</t>
         </is>
       </c>
     </row>
@@ -3912,102 +3912,102 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3798</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>8,28%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>692</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4435</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3529</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>1,3%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>8,35%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>6,65%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>1299</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>3704</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>4257</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>8,08%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>1299</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>4133</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -4020,107 +4020,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3906</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,52%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>624</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3721</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3314</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>8,12%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>624</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3123</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -4246,57 +4246,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>45853</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>45853</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>45853</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>53083</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>53083</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>53083</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>45853</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>45853</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>45853</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4363,72 +4363,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>132745</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>121060</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>144919</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>58,04%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>52,93%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>63,36%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>119548</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>108181</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>131865</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>106278</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>129882</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>58,19%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>52,66%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>64,18%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>132745</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>120938</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>144448</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>58,04%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>234767</t>
+          <t>235734</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>270033</t>
+          <t>269611</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>62,1%</t>
         </is>
       </c>
     </row>
@@ -4476,72 +4476,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>84082</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>72948</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>96244</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>36,76%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>31,89%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>42,08%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>79509</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>68465</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>91096</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>68065</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>91816</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>38,7%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>33,32%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>44,34%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>84082</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>72015</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>95770</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>36,76%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>145886</t>
+          <t>147076</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>180138</t>
+          <t>180704</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,62%</t>
         </is>
       </c>
     </row>
@@ -4589,72 +4589,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7961</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4254</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>13345</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3,48%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>5,83%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>3453</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1277</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>7650</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1274</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>7999</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>1,68%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,62%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>3,72%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>7961</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>4316</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>13182</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6881</t>
+          <t>6933</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>18112</t>
+          <t>18399</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -4707,67 +4707,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>1896</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>579</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5822</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>2283</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>693</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6503</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>696</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6161</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,11%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1896</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>577</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5159</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1473</t>
+          <t>1531</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8548</t>
+          <t>8443</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -4815,72 +4815,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2039</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>604</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5626</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>656</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3070</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3968</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>2039</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>603</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>5857</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>685</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6311</t>
+          <t>6879</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -4928,57 +4928,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>228723</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>228723</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>228723</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>294</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>205449</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>205449</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>205449</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>334</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>228723</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>228723</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>228723</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5045,72 +5045,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>33388</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>27576</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>39168</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>57,63%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>47,6%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>67,61%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>38735</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>31478</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>44835</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>32451</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>45128</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>61,08%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>49,64%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>70,7%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>33388</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>27205</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>39103</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>57,63%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>62569</t>
+          <t>63016</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>80810</t>
+          <t>81095</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>66,83%</t>
         </is>
       </c>
     </row>
@@ -5158,72 +5158,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>20906</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>15473</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>26774</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>36,09%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>26,71%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>46,22%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>20947</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>14667</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>27484</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>14999</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>27629</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>33,03%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>23,13%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>43,34%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>20906</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>15486</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>27072</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>36,09%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>43,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>33522</t>
+          <t>33488</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>50327</t>
+          <t>51363</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>42,33%</t>
         </is>
       </c>
     </row>
@@ -5276,67 +5276,67 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>3639</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1372</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>7944</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>6,28%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>13,71%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
           <t>3736</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1413</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>7914</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>1391</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>8058</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>5,89%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>12,48%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>3639</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>1414</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>7728</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>6,28%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3740</t>
+          <t>3782</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>13083</t>
+          <t>12934</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
@@ -5610,57 +5610,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>57933</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>57933</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>57933</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>63418</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>63418</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>63418</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>57933</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>57933</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>57933</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5727,107 +5727,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>188478</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>174244</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>200977</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>56,68%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>52,4%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>60,44%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>190178</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>176647</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>205297</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>175644</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>203893</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>59,07%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>54,87%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>63,77%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>188478</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>173078</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>202939</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>56,68%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
+          <t>63,33%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>548</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>378656</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>358565</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>399446</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>57,86%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>54,79%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
           <t>61,03%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>548</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>378656</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>357244</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>399052</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>57,86%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>54,59%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>60,97%</t>
         </is>
       </c>
     </row>
@@ -5840,72 +5840,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>127265</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>113764</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>142111</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>38,27%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>34,21%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>42,74%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>170</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>120953</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>106485</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>135861</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>107417</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>136276</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>37,57%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>33,07%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>42,2%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>127265</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>112876</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>141458</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>38,27%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>228213</t>
+          <t>229628</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>269308</t>
+          <t>269782</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>41,22%</t>
         </is>
       </c>
     </row>
@@ -5953,107 +5953,107 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>12207</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>7598</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>19282</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>3,67%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>5,8%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>7880</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>4471</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>13748</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>4112</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>13846</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>2,45%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>4,3%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>20087</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>13756</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>27959</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
         <is>
           <t>4,27%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>12207</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>7347</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>19014</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>3,67%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>5,72%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>20087</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>13449</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>28805</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>3,07%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>2,05%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -6066,72 +6066,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>2520</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>5734</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>2283</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>691</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>6061</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>6131</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,71%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,21%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>2520</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>686</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>6229</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9660</t>
+          <t>9162</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -6179,72 +6179,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>2039</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>604</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>5482</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>656</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>3787</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3318</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>2039</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>611</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>6302</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>686</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6781</t>
+          <t>6771</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -6292,57 +6292,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>484</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>332508</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>332508</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>332508</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>457</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>321950</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>321950</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>321950</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>332508</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>332508</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>332508</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6455,13 +6455,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse alegre, percibida por el adulto en 2016 (tasa de respuesta: 99,02%)</t>
+          <t>Menores según la frecuencia de sentirse alegre, percibida por el/la adulto/a [KIDSCREEN 20] en 2016 (tasa de respuesta: 99,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6472,7 +6472,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6640,72 +6640,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>21579</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>16317</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>26122</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>58,9%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>44,53%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>71,3%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>18122</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>13678</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>22564</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>13638</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>22757</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>56,96%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>42,99%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>70,92%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>21579</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>16545</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>26376</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>58,9%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32681</t>
+          <t>32860</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46320</t>
+          <t>45863</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>67,0%</t>
         </is>
       </c>
     </row>
@@ -6753,72 +6753,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>13505</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9070</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>18722</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>36,86%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>24,75%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>51,1%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>11315</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>6883</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>15497</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>7119</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>16347</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>35,57%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>21,63%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>48,71%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>13505</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>9138</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>18524</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>36,86%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18284</t>
+          <t>18552</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31280</t>
+          <t>31709</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>46,32%</t>
         </is>
       </c>
     </row>
@@ -6866,72 +6866,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1554</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5056</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>4,24%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>13,8%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>2377</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>574</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6911</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>569</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>6098</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>7,47%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>21,72%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1554</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>5892</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>4,24%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1470</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9015</t>
+          <t>8454</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -7205,57 +7205,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>36638</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>36638</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>36638</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>31814</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>31814</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>31814</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>36638</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>36638</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>36638</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7322,72 +7322,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>133779</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>120115</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>146912</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>54,24%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>48,7%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>59,56%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>197</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>136928</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>123157</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>149790</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>123588</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>149108</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>54,65%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>49,15%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>59,78%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>133779</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>120911</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>146853</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>54,24%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>251849</t>
+          <t>249693</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>286980</t>
+          <t>288085</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>57,94%</t>
         </is>
       </c>
     </row>
@@ -7435,72 +7435,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>101224</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>88721</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>114752</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>41,04%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>35,97%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>46,52%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>142</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>99598</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>87927</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>112790</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>87235</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>113414</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>39,75%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>35,09%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>45,02%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>101224</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>88987</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>114234</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>41,04%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>184517</t>
+          <t>183368</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>219289</t>
+          <t>219583</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,16%</t>
         </is>
       </c>
     </row>
@@ -7548,72 +7548,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9572</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5408</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>15531</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3,88%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>6,3%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>11619</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>7099</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>17971</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>7175</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>18610</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>4,64%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,83%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>7,17%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>9572</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>5473</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>15646</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>3,88%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>14459</t>
+          <t>14349</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>28840</t>
+          <t>29411</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -7666,102 +7666,102 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2912</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>993</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4999</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5227</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>717</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1710</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3609</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>6116</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>5590</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -7779,94 +7779,94 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>1370</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4685</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>1421</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5045</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4424</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,57%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,01%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1370</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>4167</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>2792</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>724</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>7023</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>0,56%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>2792</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>723</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>6978</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,15%</t>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -7887,57 +7887,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>246662</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>246662</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>246662</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>360</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>250559</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>250559</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>250559</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>337</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>246662</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>246662</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>246662</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8004,72 +8004,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>45820</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>38487</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>53320</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>58,7%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>49,3%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>68,3%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>35367</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>29170</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>42487</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>28308</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>42379</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>47,54%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>39,21%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>57,11%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>45820</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>38184</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>52852</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>58,7%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>70674</t>
+          <t>70688</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>91505</t>
+          <t>93536</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>61,35%</t>
         </is>
       </c>
     </row>
@@ -8117,72 +8117,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>31570</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>24157</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>38588</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>40,44%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>30,95%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>49,43%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>35806</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>28544</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>42061</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>28990</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>43027</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>48,13%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>38,37%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>56,54%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>31570</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>24698</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>39587</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>40,44%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>57,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>56687</t>
+          <t>55532</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>77920</t>
+          <t>77885</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>51,09%</t>
         </is>
       </c>
     </row>
@@ -8230,72 +8230,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>671</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>3940</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>5,05%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>2519</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>648</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>6396</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>5741</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>3,39%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>8,6%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>671</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>3375</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7047</t>
+          <t>7641</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -8456,107 +8456,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>706</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>3544</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3525</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,95%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>4,76%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>4,74%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>706</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>3594</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>706</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>3556</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -8569,57 +8569,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>78061</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>78061</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>78061</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>74398</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>74398</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>74398</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>78061</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>78061</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>78061</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8691,67 +8691,67 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>201178</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>184612</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>217591</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>55,67%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>51,09%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>60,21%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
           <t>190417</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>173862</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>207589</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>174796</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>207005</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>53,37%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>48,73%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>58,19%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>201178</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>185167</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>216944</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>55,67%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>58,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>368485</t>
+          <t>367057</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>416148</t>
+          <t>413429</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>57,57%</t>
         </is>
       </c>
     </row>
@@ -8799,72 +8799,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>146300</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>131269</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>164127</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>40,49%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>36,33%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>45,42%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>208</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>146720</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>129555</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>161904</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>130623</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>162286</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>41,12%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>36,31%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>45,38%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>146300</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>131102</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>162355</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>40,49%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>270428</t>
+          <t>272134</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>315271</t>
+          <t>316863</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>44,12%</t>
         </is>
       </c>
     </row>
@@ -8912,72 +8912,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>11796</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>7207</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>18543</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>1,99%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>5,13%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>16515</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>10884</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>24899</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>10500</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>23544</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>4,63%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>3,05%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>6,98%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>11796</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>6901</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>18660</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>3,26%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>20622</t>
+          <t>20541</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>38192</t>
+          <t>37598</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -9030,102 +9030,102 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>3595</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
           <t>993</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>4629</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>4972</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,28%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>717</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>1710</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>3620</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>6203</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>6008</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -9138,107 +9138,107 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>1370</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>5359</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>2128</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>661</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>5815</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>660</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>5718</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,6%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>3498</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>1374</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>7891</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>1370</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>4740</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>3498</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>1361</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>7700</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -9251,57 +9251,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>496</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>361361</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>361361</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>361361</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>510</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>356772</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>356772</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>356772</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>496</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>361361</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>361361</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>361361</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
